--- a/docs/참고/인허가/사운드1/[참고] Sound1 입력 음압 대비 ADC 출력 테이블.xlsx
+++ b/docs/참고/인허가/사운드1/[참고] Sound1 입력 음압 대비 ADC 출력 테이블.xlsx
@@ -495,7 +495,7 @@
         <is>
           <t>1.5세대와 Sound1 은 같은 스펙의 마이크를 쓴다. 그래서 1.5세대 테이블의 생성 규칙을 그대로 두고 Sound1 의 실측 감쇠만 반영했다.
 ADC = round(262143 x 10^((dB SPL - 120 + 감쇠) / 20)),  262143 = 2^18 - 1
-감쇠는 고음압 평탄 구간(80~110 dB SPL) 실측 평균이다. PCB 상태 -3.644 dB (5 시료), 기구 조립 -5.593 dB (3 시료).</t>
+감쇠는 고음압 평탄 구간(80~110 dB SPL) 실측 평균이다. PCB 상태 -3.644 dB (5 시료), 기구 조립 -7.500 dB (3 시료).</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
         <v>5</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -581,7 +581,7 @@
         <v>6</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -598,7 +598,7 @@
         <v>6</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -615,7 +615,7 @@
         <v>7</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -632,7 +632,7 @@
         <v>8</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -649,7 +649,7 @@
         <v>9</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -666,7 +666,7 @@
         <v>10</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -683,7 +683,7 @@
         <v>12</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -700,7 +700,7 @@
         <v>13</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -717,7 +717,7 @@
         <v>15</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -734,7 +734,7 @@
         <v>17</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -751,7 +751,7 @@
         <v>19</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
@@ -768,7 +768,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
@@ -785,7 +785,7 @@
         <v>24</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
@@ -802,7 +802,7 @@
         <v>27</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25">
@@ -819,7 +819,7 @@
         <v>30</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
@@ -836,7 +836,7 @@
         <v>34</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27">
@@ -853,7 +853,7 @@
         <v>38</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28">
@@ -870,7 +870,7 @@
         <v>43</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29">
@@ -887,7 +887,7 @@
         <v>48</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30">
@@ -904,7 +904,7 @@
         <v>54</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31">
@@ -921,7 +921,7 @@
         <v>61</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32">
@@ -938,7 +938,7 @@
         <v>68</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33">
@@ -955,7 +955,7 @@
         <v>76</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34">
@@ -972,7 +972,7 @@
         <v>86</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>69</v>
+        <v>55</v>
       </c>
     </row>
     <row r="35">
@@ -989,7 +989,7 @@
         <v>96</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
     </row>
     <row r="36">
@@ -1006,7 +1006,7 @@
         <v>108</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>86</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37">
@@ -1023,7 +1023,7 @@
         <v>121</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>97</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38">
@@ -1040,7 +1040,7 @@
         <v>136</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>109</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39">
@@ -1057,7 +1057,7 @@
         <v>153</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>122</v>
+        <v>98</v>
       </c>
     </row>
     <row r="40">
@@ -1074,7 +1074,7 @@
         <v>172</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>137</v>
+        <v>110</v>
       </c>
     </row>
     <row r="41">
@@ -1091,7 +1091,7 @@
         <v>193</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>154</v>
+        <v>124</v>
       </c>
     </row>
     <row r="42">
@@ -1108,7 +1108,7 @@
         <v>216</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="43">
@@ -1125,7 +1125,7 @@
         <v>243</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>194</v>
+        <v>156</v>
       </c>
     </row>
     <row r="44">
@@ -1142,7 +1142,7 @@
         <v>273</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>218</v>
+        <v>175</v>
       </c>
     </row>
     <row r="45">
@@ -1159,7 +1159,7 @@
         <v>306</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>244</v>
+        <v>196</v>
       </c>
     </row>
     <row r="46">
@@ -1176,7 +1176,7 @@
         <v>343</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="47">
@@ -1193,7 +1193,7 @@
         <v>385</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>308</v>
+        <v>247</v>
       </c>
     </row>
     <row r="48">
@@ -1210,7 +1210,7 @@
         <v>432</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>345</v>
+        <v>277</v>
       </c>
     </row>
     <row r="49">
@@ -1227,7 +1227,7 @@
         <v>485</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>388</v>
+        <v>311</v>
       </c>
     </row>
     <row r="50">
@@ -1244,7 +1244,7 @@
         <v>544</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>435</v>
+        <v>349</v>
       </c>
     </row>
     <row r="51">
@@ -1261,7 +1261,7 @@
         <v>611</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>488</v>
+        <v>392</v>
       </c>
     </row>
     <row r="52">
@@ -1278,7 +1278,7 @@
         <v>686</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>548</v>
+        <v>440</v>
       </c>
     </row>
     <row r="53">
@@ -1295,7 +1295,7 @@
         <v>769</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>615</v>
+        <v>493</v>
       </c>
     </row>
     <row r="54">
@@ -1312,7 +1312,7 @@
         <v>863</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>690</v>
+        <v>554</v>
       </c>
     </row>
     <row r="55">
@@ -1329,7 +1329,7 @@
         <v>969</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>774</v>
+        <v>621</v>
       </c>
     </row>
     <row r="56">
@@ -1346,7 +1346,7 @@
         <v>1087</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>868</v>
+        <v>697</v>
       </c>
     </row>
     <row r="57">
@@ -1363,7 +1363,7 @@
         <v>1219</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>974</v>
+        <v>782</v>
       </c>
     </row>
     <row r="58">
@@ -1380,7 +1380,7 @@
         <v>1368</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>1093</v>
+        <v>878</v>
       </c>
     </row>
     <row r="59">
@@ -1397,7 +1397,7 @@
         <v>1535</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>1227</v>
+        <v>985</v>
       </c>
     </row>
     <row r="60">
@@ -1414,7 +1414,7 @@
         <v>1723</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>1376</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="61">
@@ -1431,7 +1431,7 @@
         <v>1933</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1544</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="62">
@@ -1448,7 +1448,7 @@
         <v>2169</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>1733</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="63">
@@ -1465,7 +1465,7 @@
         <v>2434</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>1944</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="64">
@@ -1482,7 +1482,7 @@
         <v>2731</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>2182</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="65">
@@ -1499,7 +1499,7 @@
         <v>3064</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>2448</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="66">
@@ -1516,7 +1516,7 @@
         <v>3438</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>2747</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="67">
@@ -1533,7 +1533,7 @@
         <v>3857</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>3082</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="68">
@@ -1550,7 +1550,7 @@
         <v>4328</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>3458</v>
+        <v>2776</v>
       </c>
     </row>
     <row r="69">
@@ -1567,7 +1567,7 @@
         <v>4856</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>3880</v>
+        <v>3115</v>
       </c>
     </row>
     <row r="70">
@@ -1584,7 +1584,7 @@
         <v>5449</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>4353</v>
+        <v>3495</v>
       </c>
     </row>
     <row r="71">
@@ -1601,7 +1601,7 @@
         <v>6114</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>4885</v>
+        <v>3922</v>
       </c>
     </row>
     <row r="72">
@@ -1618,7 +1618,7 @@
         <v>6860</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>5481</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="73">
@@ -1635,7 +1635,7 @@
         <v>7697</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>6150</v>
+        <v>4937</v>
       </c>
     </row>
     <row r="74">
@@ -1652,7 +1652,7 @@
         <v>8636</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>6900</v>
+        <v>5540</v>
       </c>
     </row>
     <row r="75">
@@ -1669,7 +1669,7 @@
         <v>9690</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>7742</v>
+        <v>6216</v>
       </c>
     </row>
     <row r="76">
@@ -1686,7 +1686,7 @@
         <v>10872</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>8687</v>
+        <v>6974</v>
       </c>
     </row>
     <row r="77">
@@ -1703,7 +1703,7 @@
         <v>12199</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>9747</v>
+        <v>7825</v>
       </c>
     </row>
     <row r="78">
@@ -1720,7 +1720,7 @@
         <v>13687</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>10936</v>
+        <v>8780</v>
       </c>
     </row>
     <row r="79">
@@ -1737,7 +1737,7 @@
         <v>15358</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>12271</v>
+        <v>9852</v>
       </c>
     </row>
     <row r="80">
@@ -1754,7 +1754,7 @@
         <v>17232</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>13768</v>
+        <v>11054</v>
       </c>
     </row>
     <row r="81">
@@ -1771,7 +1771,7 @@
         <v>19334</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>15448</v>
+        <v>12403</v>
       </c>
     </row>
     <row r="82">
@@ -1788,7 +1788,7 @@
         <v>21693</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>17333</v>
+        <v>13916</v>
       </c>
     </row>
     <row r="83">
@@ -1805,7 +1805,7 @@
         <v>24340</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>19448</v>
+        <v>15614</v>
       </c>
     </row>
     <row r="84">
@@ -1822,7 +1822,7 @@
         <v>27311</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>21821</v>
+        <v>17520</v>
       </c>
     </row>
     <row r="85">
@@ -1839,7 +1839,7 @@
         <v>30643</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>24484</v>
+        <v>19657</v>
       </c>
     </row>
     <row r="86">
@@ -1856,7 +1856,7 @@
         <v>34382</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>27471</v>
+        <v>22056</v>
       </c>
     </row>
     <row r="87">
@@ -1873,7 +1873,7 @@
         <v>38577</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>30823</v>
+        <v>24747</v>
       </c>
     </row>
     <row r="88">
@@ -1890,7 +1890,7 @@
         <v>43285</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>34585</v>
+        <v>27767</v>
       </c>
     </row>
     <row r="89">
@@ -1907,7 +1907,7 @@
         <v>48566</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>38805</v>
+        <v>31155</v>
       </c>
     </row>
     <row r="90">
@@ -1924,7 +1924,7 @@
         <v>54492</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>43539</v>
+        <v>34957</v>
       </c>
     </row>
     <row r="91">
@@ -1941,7 +1941,7 @@
         <v>61141</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>48852</v>
+        <v>39222</v>
       </c>
     </row>
     <row r="92">
@@ -1958,7 +1958,7 @@
         <v>68602</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>54813</v>
+        <v>44008</v>
       </c>
     </row>
     <row r="93">
@@ -1975,7 +1975,7 @@
         <v>76972</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>61501</v>
+        <v>49378</v>
       </c>
     </row>
     <row r="94">
@@ -1992,7 +1992,7 @@
         <v>86365</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>69006</v>
+        <v>55403</v>
       </c>
     </row>
     <row r="95">
@@ -2009,7 +2009,7 @@
         <v>96903</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>77426</v>
+        <v>62163</v>
       </c>
     </row>
     <row r="96">
@@ -2026,7 +2026,7 @@
         <v>108727</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>86873</v>
+        <v>69749</v>
       </c>
     </row>
     <row r="97">
@@ -2043,7 +2043,7 @@
         <v>121993</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>97473</v>
+        <v>78259</v>
       </c>
     </row>
     <row r="98">
@@ -2060,7 +2060,7 @@
         <v>136879</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>109367</v>
+        <v>87808</v>
       </c>
     </row>
     <row r="99">
@@ -2077,7 +2077,7 @@
         <v>153581</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>122712</v>
+        <v>98523</v>
       </c>
     </row>
     <row r="100">
@@ -2094,7 +2094,7 @@
         <v>172321</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>137685</v>
+        <v>110544</v>
       </c>
     </row>
   </sheetData>
@@ -2112,7 +2112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G32"/>
+  <dimension ref="B2:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>다른 기구 시료보다 낮다. 기준 산출에서 제외</t>
+          <t>다른 기구 시료보다 낮다. 판정 기준의 하한 산정에 반영</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>홀수 음압 결측. 같은 시료 1차와 4 dB 차. 제외</t>
+          <t>홀수 음압 결측(4 점). 같은 시료 1차와 4 dB 차</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>가장 낮다. 2차 재측정에서 4 dB 개선. 제외</t>
+          <t>실측 최저. 판정 기준의 «하한» 이 된다. 2차 재측정에서 4 dB 개선된 것으로 보아 조립 편차다</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
     <row r="19">
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>PCB 상태 평균</t>
+          <t>PCB 상태 평균 (참조용)</t>
         </is>
       </c>
       <c r="C19" s="9" t="n">
@@ -2468,117 +2468,185 @@
     <row r="20">
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>기구 조립 평균 (이상 3 시료 제외)</t>
+          <t>기구 조립 판정 기준</t>
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>-5.593</v>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>3 시료</t>
-        </is>
-      </c>
+        <v>-7.5</v>
+      </c>
+      <c r="D20" s="9" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>기구에 의한 추가 감쇠</t>
+          <t xml:space="preserve">  상한 (조립 감쇠 거의 없는 극단)</t>
         </is>
       </c>
       <c r="C21" s="9" t="n">
-        <v>-1.949</v>
+        <v>-3.566</v>
       </c>
       <c r="D21" s="9" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>기구 조립 전체 평균 (참고)</t>
+          <t xml:space="preserve">  하한 (실측 최저 500C-1차)</t>
         </is>
       </c>
       <c r="C22" s="9" t="n">
+        <v>-11.433</v>
+      </c>
+      <c r="D22" s="9" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  상·하한 여유 (허용 +-5 dB)</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>1.066</v>
+      </c>
+      <c r="D23" s="9" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  이 기준의 통과 하한</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="D24" s="9" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>기구 조립 실측 평균 (참고, 편차 큰 3 제외)</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>-5.593</v>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>3 시료</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>기구 조립 실측 평균 (참고, 전체 6)</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="n">
         <v>-7.075</v>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>6 시료</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="7" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>판단 근거</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>1. 1.5세대와 Sound1 은 같은 스펙의 마이크를 쓴다. 감도 차이는 일정한 dB 차로 나타난다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>2. 그래서 1.5세대 테이블의 생성 규칙을 그대로 두고 감쇠 항만 더했다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>3. 감쇠는 고음압 평탄 구간(80~110 dB SPL)에서 구했다. 저음압은 잡음 바닥 탓에 흔들려 그대로 쓰면 오히려 틀린다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>4. PCB 상태 5 시료는 -3.57 ~ -3.75 dB 로 매우 고르다(범위 0.18 dB). 기준으로 삼기에 충분하다.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>5. 기구 조립은 500C-1차 -11.43, 500C-2차 -7.48, 500D -6.76 dB 로 낮았다. 같은 500C 가 1차와 2차에서 4 dB 나 달라진 것은 조립 편차를 가리킨다. 셋을 제외했다.</t>
+          <t>1. 1.5세대와 Sound1 은 같은 스펙의 마이크를 쓴다. 감도 차이는 일정한 dB 차로 나타난다.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>6. 남은 3 시료(500A -5.97, 500E -5.15, 500F -5.65)로 기준을 잡았다.</t>
+          <t>2. 그래서 1.5세대 테이블의 생성 규칙을 그대로 두고 감쇠 항만 더했다.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>7. 기구에 의한 추가 감쇠는 약 1.95 dB 다.</t>
+          <t>3. 감쇠는 고음압 평탄 구간(80~110 dB SPL)에서 구했다. 저음압은 잡음 바닥 탓에 흔들려 그대로 쓰면 오히려 틀린다.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>8. 원본 시트에서 측정값이 헤더보다 한 행 아래에 있어 바로잡아 읽었다. 음압 값 14 개와 측정 행 14 개가 맞고, 4 행에는 값이 없으며 18 행에는 음압이 없다.</t>
+          <t>4. PCB 상태 5 시료는 -3.57 ~ -3.75 dB 로 매우 고르다(범위 0.18 dB). 기준으로 삼기에 충분하다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>5. 기구 조립은 500C-1차 -11.43, 500C-2차 -7.48, 500D -6.76 dB 로 낮았다. 같은 500C 가 1차와 2차에서 4 dB 나 달라진 것은 시료가 아니라 조립 편차를 가리킨다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>6. 이 셋을 «불량» 으로 빼지 않고 하한 산정에 썼다. 시험 판정 기준은 대표 성능이 아니라 실제로 나올 수 있는 범위를 담아야 하기 때문이다. 11 시료를 모두 썼다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>7. 판정용 기준은 «실측 전체가 허용 폭 안에 담기는 중심» 으로 잡았다. 조립은 감쇠만 시키므로 상한은 조립 감쇠가 거의 없는 극단(PCB 상태)이고 하한은 실측 최저다. 그 중앙 -7.500 에서 상·하한 여유가 각 1.07 dB 로 대칭이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>8. 이 기준이면 실측 6 시료가 모두 통과하고, 500C-1차(-11.43)보다 1.07 dB 더 나쁜 -12.50 dB 까지 받아 준다. PCB 상태(-3.57)도 여유 3.93 으로 담긴다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>9. 기준을 이보다 낮추면 하한은 넓어지지만 상한이 깨진다. 예를 들어 500D 와 500C-1차의 중간(-9.096)으로 잡으면 조립 감쇠가 거의 없는 개체가 위로 탈락한다(상한 여유 -0.53).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>10. 감수하는 것이 있다. 500C-1차 같은 조립 불량도 통과하므로 이 시험만으로는 조립 불량을 걸러내지 못한다. 조립 품질은 별도 수단으로 보아야 한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>11. 원본 시트에서 측정값이 헤더보다 한 행 아래에 있어 바로잡아 읽었다. 음압 값 14 개와 측정 행 14 개가 맞고, 4 행에는 값이 없으며 18 행에는 음압이 없다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B28:G28"/>
+  <mergeCells count="11">
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="B37:G37"/>
     <mergeCell ref="B31:G31"/>
-    <mergeCell ref="B27:G27"/>
     <mergeCell ref="B32:G32"/>
-    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="B35:G35"/>
     <mergeCell ref="B30:G30"/>
     <mergeCell ref="B29:G29"/>
-    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="B33:G33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/참고/인허가/사운드1/[참고] Sound1 입력 음압 대비 ADC 출력 테이블.xlsx
+++ b/docs/참고/인허가/사운드1/[참고] Sound1 입력 음압 대비 ADC 출력 테이블.xlsx
@@ -495,7 +495,7 @@
         <is>
           <t>1.5세대와 Sound1 은 같은 스펙의 마이크를 쓴다. 그래서 1.5세대 테이블의 생성 규칙을 그대로 두고 Sound1 의 실측 감쇠만 반영했다.
 ADC = round(262143 x 10^((dB SPL - 120 + 감쇠) / 20)),  262143 = 2^18 - 1
-감쇠는 고음압 평탄 구간(80~110 dB SPL) 실측 평균이다. PCB 상태 -3.644 dB (5 시료), 기구 조립 -7.500 dB (3 시료).</t>
+감쇠는 고음압 평탄 구간(80~110 dB SPL) 실측 평균이다. PCB 상태 -3.644 dB (5 시료), 기구 조립 -8.293 dB (3 시료).</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
         <v>4</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -649,7 +649,7 @@
         <v>9</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -717,7 +717,7 @@
         <v>15</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -734,7 +734,7 @@
         <v>17</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -751,7 +751,7 @@
         <v>19</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22">
@@ -768,7 +768,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
@@ -785,7 +785,7 @@
         <v>24</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
@@ -802,7 +802,7 @@
         <v>27</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
@@ -819,7 +819,7 @@
         <v>30</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26">
@@ -836,7 +836,7 @@
         <v>34</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27">
@@ -853,7 +853,7 @@
         <v>38</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28">
@@ -870,7 +870,7 @@
         <v>43</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29">
@@ -887,7 +887,7 @@
         <v>48</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30">
@@ -904,7 +904,7 @@
         <v>54</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31">
@@ -921,7 +921,7 @@
         <v>61</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32">
@@ -938,7 +938,7 @@
         <v>68</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="33">
@@ -955,7 +955,7 @@
         <v>76</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34">
@@ -972,7 +972,7 @@
         <v>86</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35">
@@ -989,7 +989,7 @@
         <v>96</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="36">
@@ -1006,7 +1006,7 @@
         <v>108</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37">
@@ -1023,7 +1023,7 @@
         <v>121</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38">
@@ -1040,7 +1040,7 @@
         <v>136</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="39">
@@ -1057,7 +1057,7 @@
         <v>153</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40">
@@ -1074,7 +1074,7 @@
         <v>172</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41">
@@ -1091,7 +1091,7 @@
         <v>193</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>124</v>
+        <v>113</v>
       </c>
     </row>
     <row r="42">
@@ -1108,7 +1108,7 @@
         <v>216</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>139</v>
+        <v>127</v>
       </c>
     </row>
     <row r="43">
@@ -1125,7 +1125,7 @@
         <v>243</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>156</v>
+        <v>142</v>
       </c>
     </row>
     <row r="44">
@@ -1142,7 +1142,7 @@
         <v>273</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>175</v>
+        <v>159</v>
       </c>
     </row>
     <row r="45">
@@ -1159,7 +1159,7 @@
         <v>306</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>196</v>
+        <v>179</v>
       </c>
     </row>
     <row r="46">
@@ -1176,7 +1176,7 @@
         <v>343</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>220</v>
+        <v>201</v>
       </c>
     </row>
     <row r="47">
@@ -1193,7 +1193,7 @@
         <v>385</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>247</v>
+        <v>225</v>
       </c>
     </row>
     <row r="48">
@@ -1210,7 +1210,7 @@
         <v>432</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>277</v>
+        <v>253</v>
       </c>
     </row>
     <row r="49">
@@ -1227,7 +1227,7 @@
         <v>485</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>311</v>
+        <v>284</v>
       </c>
     </row>
     <row r="50">
@@ -1244,7 +1244,7 @@
         <v>544</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>349</v>
+        <v>319</v>
       </c>
     </row>
     <row r="51">
@@ -1261,7 +1261,7 @@
         <v>611</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>392</v>
+        <v>358</v>
       </c>
     </row>
     <row r="52">
@@ -1278,7 +1278,7 @@
         <v>686</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>440</v>
+        <v>401</v>
       </c>
     </row>
     <row r="53">
@@ -1295,7 +1295,7 @@
         <v>769</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>493</v>
+        <v>450</v>
       </c>
     </row>
     <row r="54">
@@ -1312,7 +1312,7 @@
         <v>863</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>554</v>
+        <v>505</v>
       </c>
     </row>
     <row r="55">
@@ -1329,7 +1329,7 @@
         <v>969</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>621</v>
+        <v>567</v>
       </c>
     </row>
     <row r="56">
@@ -1346,7 +1346,7 @@
         <v>1087</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>697</v>
+        <v>636</v>
       </c>
     </row>
     <row r="57">
@@ -1363,7 +1363,7 @@
         <v>1219</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>782</v>
+        <v>714</v>
       </c>
     </row>
     <row r="58">
@@ -1380,7 +1380,7 @@
         <v>1368</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>878</v>
+        <v>801</v>
       </c>
     </row>
     <row r="59">
@@ -1397,7 +1397,7 @@
         <v>1535</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>985</v>
+        <v>899</v>
       </c>
     </row>
     <row r="60">
@@ -1414,7 +1414,7 @@
         <v>1723</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>1105</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="61">
@@ -1431,7 +1431,7 @@
         <v>1933</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1240</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="62">
@@ -1448,7 +1448,7 @@
         <v>2169</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>1391</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="63">
@@ -1465,7 +1465,7 @@
         <v>2434</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>1561</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="64">
@@ -1482,7 +1482,7 @@
         <v>2731</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>1752</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="65">
@@ -1499,7 +1499,7 @@
         <v>3064</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>1965</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="66">
@@ -1516,7 +1516,7 @@
         <v>3438</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>2205</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="67">
@@ -1533,7 +1533,7 @@
         <v>3857</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>2474</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="68">
@@ -1550,7 +1550,7 @@
         <v>4328</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>2776</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="69">
@@ -1567,7 +1567,7 @@
         <v>4856</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>3115</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="70">
@@ -1584,7 +1584,7 @@
         <v>5449</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>3495</v>
+        <v>3190</v>
       </c>
     </row>
     <row r="71">
@@ -1601,7 +1601,7 @@
         <v>6114</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>3922</v>
+        <v>3580</v>
       </c>
     </row>
     <row r="72">
@@ -1618,7 +1618,7 @@
         <v>6860</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>4400</v>
+        <v>4016</v>
       </c>
     </row>
     <row r="73">
@@ -1635,7 +1635,7 @@
         <v>7697</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>4937</v>
+        <v>4507</v>
       </c>
     </row>
     <row r="74">
@@ -1652,7 +1652,7 @@
         <v>8636</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>5540</v>
+        <v>5056</v>
       </c>
     </row>
     <row r="75">
@@ -1669,7 +1669,7 @@
         <v>9690</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>6216</v>
+        <v>5673</v>
       </c>
     </row>
     <row r="76">
@@ -1686,7 +1686,7 @@
         <v>10872</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>6974</v>
+        <v>6366</v>
       </c>
     </row>
     <row r="77">
@@ -1703,7 +1703,7 @@
         <v>12199</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>7825</v>
+        <v>7143</v>
       </c>
     </row>
     <row r="78">
@@ -1720,7 +1720,7 @@
         <v>13687</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>8780</v>
+        <v>8014</v>
       </c>
     </row>
     <row r="79">
@@ -1737,7 +1737,7 @@
         <v>15358</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>9852</v>
+        <v>8992</v>
       </c>
     </row>
     <row r="80">
@@ -1754,7 +1754,7 @@
         <v>17232</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>11054</v>
+        <v>10089</v>
       </c>
     </row>
     <row r="81">
@@ -1771,7 +1771,7 @@
         <v>19334</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>12403</v>
+        <v>11321</v>
       </c>
     </row>
     <row r="82">
@@ -1788,7 +1788,7 @@
         <v>21693</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>13916</v>
+        <v>12702</v>
       </c>
     </row>
     <row r="83">
@@ -1805,7 +1805,7 @@
         <v>24340</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>15614</v>
+        <v>14252</v>
       </c>
     </row>
     <row r="84">
@@ -1822,7 +1822,7 @@
         <v>27311</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>17520</v>
+        <v>15991</v>
       </c>
     </row>
     <row r="85">
@@ -1839,7 +1839,7 @@
         <v>30643</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>19657</v>
+        <v>17942</v>
       </c>
     </row>
     <row r="86">
@@ -1856,7 +1856,7 @@
         <v>34382</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>22056</v>
+        <v>20132</v>
       </c>
     </row>
     <row r="87">
@@ -1873,7 +1873,7 @@
         <v>38577</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>24747</v>
+        <v>22588</v>
       </c>
     </row>
     <row r="88">
@@ -1890,7 +1890,7 @@
         <v>43285</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>27767</v>
+        <v>25344</v>
       </c>
     </row>
     <row r="89">
@@ -1907,7 +1907,7 @@
         <v>48566</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>31155</v>
+        <v>28437</v>
       </c>
     </row>
     <row r="90">
@@ -1924,7 +1924,7 @@
         <v>54492</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>34957</v>
+        <v>31907</v>
       </c>
     </row>
     <row r="91">
@@ -1941,7 +1941,7 @@
         <v>61141</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>39222</v>
+        <v>35800</v>
       </c>
     </row>
     <row r="92">
@@ -1958,7 +1958,7 @@
         <v>68602</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>44008</v>
+        <v>40168</v>
       </c>
     </row>
     <row r="93">
@@ -1975,7 +1975,7 @@
         <v>76972</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>49378</v>
+        <v>45070</v>
       </c>
     </row>
     <row r="94">
@@ -1992,7 +1992,7 @@
         <v>86365</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>55403</v>
+        <v>50569</v>
       </c>
     </row>
     <row r="95">
@@ -2009,7 +2009,7 @@
         <v>96903</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>62163</v>
+        <v>56739</v>
       </c>
     </row>
     <row r="96">
@@ -2026,7 +2026,7 @@
         <v>108727</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>69749</v>
+        <v>63663</v>
       </c>
     </row>
     <row r="97">
@@ -2043,7 +2043,7 @@
         <v>121993</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>78259</v>
+        <v>71431</v>
       </c>
     </row>
     <row r="98">
@@ -2060,7 +2060,7 @@
         <v>136879</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>87808</v>
+        <v>80147</v>
       </c>
     </row>
     <row r="99">
@@ -2077,7 +2077,7 @@
         <v>153581</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>98523</v>
+        <v>89926</v>
       </c>
     </row>
     <row r="100">
@@ -2094,7 +2094,7 @@
         <v>172321</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>110544</v>
+        <v>100899</v>
       </c>
     </row>
   </sheetData>
@@ -2112,7 +2112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G39"/>
+  <dimension ref="B2:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2315,7 +2315,11 @@
       <c r="F11" s="4" t="n">
         <v>0.2</v>
       </c>
-      <c r="G11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>기구 조립 실측 최고. 판정 기준의 «상한» 이 된다</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="4" t="inlineStr">
@@ -2361,7 +2365,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>다른 기구 시료보다 낮다. 판정 기준의 하한 산정에 반영</t>
+          <t>다른 기구 시료보다 낮다. 제외하지 않고 판정 범위 안에 담았다</t>
         </is>
       </c>
     </row>
@@ -2472,18 +2476,18 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>-7.5</v>
+        <v>-8.292999999999999</v>
       </c>
       <c r="D20" s="9" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  상한 (조립 감쇠 거의 없는 극단)</t>
+          <t xml:space="preserve">  상한 (실측 최고 500E)</t>
         </is>
       </c>
       <c r="C21" s="9" t="n">
-        <v>-3.566</v>
+        <v>-5.153</v>
       </c>
       <c r="D21" s="9" t="inlineStr"/>
     </row>
@@ -2505,7 +2509,7 @@
         </is>
       </c>
       <c r="C23" s="9" t="n">
-        <v>1.066</v>
+        <v>1.86</v>
       </c>
       <c r="D23" s="9" t="inlineStr"/>
     </row>
@@ -2516,136 +2520,155 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>-12.5</v>
+        <v>-13.293</v>
       </c>
       <c r="D24" s="9" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>기구 조립 실측 평균 (참고, 편차 큰 3 제외)</t>
+          <t xml:space="preserve">  조립 감쇠 0 인 극단(PCB 최고)의 여유</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>-5.593</v>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>3 시료</t>
-        </is>
-      </c>
+        <v>0.273</v>
+      </c>
+      <c r="D25" s="9" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="B26" s="8" t="inlineStr">
         <is>
+          <t>기구 조립 실측 평균 (참고, 편차 큰 3 제외)</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>-5.593</v>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>3 시료</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="8" t="inlineStr">
+        <is>
           <t>기구 조립 실측 평균 (참고, 전체 6)</t>
         </is>
       </c>
-      <c r="C26" s="9" t="n">
+      <c r="C27" s="9" t="n">
         <v>-7.075</v>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>6 시료</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="7" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>판단 근거</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>1. 1.5세대와 Sound1 은 같은 스펙의 마이크를 쓴다. 감도 차이는 일정한 dB 차로 나타난다.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>2. 그래서 1.5세대 테이블의 생성 규칙을 그대로 두고 감쇠 항만 더했다.</t>
+          <t>1. 1.5세대와 Sound1 은 같은 스펙의 마이크를 쓴다. 감도 차이는 일정한 dB 차로 나타난다.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>3. 감쇠는 고음압 평탄 구간(80~110 dB SPL)에서 구했다. 저음압은 잡음 바닥 탓에 흔들려 그대로 쓰면 오히려 틀린다.</t>
+          <t>2. 그래서 1.5세대 테이블의 생성 규칙을 그대로 두고 감쇠 항만 더했다.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>4. PCB 상태 5 시료는 -3.57 ~ -3.75 dB 로 매우 고르다(범위 0.18 dB). 기준으로 삼기에 충분하다.</t>
+          <t>3. 감쇠는 고음압 평탄 구간(80~110 dB SPL)에서 구했다. 저음압은 잡음 바닥 탓에 흔들려 그대로 쓰면 오히려 틀린다.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>5. 기구 조립은 500C-1차 -11.43, 500C-2차 -7.48, 500D -6.76 dB 로 낮았다. 같은 500C 가 1차와 2차에서 4 dB 나 달라진 것은 시료가 아니라 조립 편차를 가리킨다.</t>
+          <t>4. PCB 상태 5 시료는 -3.57 ~ -3.75 dB 로 매우 고르다(범위 0.18 dB). 기준으로 삼기에 충분하다.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>6. 이 셋을 «불량» 으로 빼지 않고 하한 산정에 썼다. 시험 판정 기준은 대표 성능이 아니라 실제로 나올 수 있는 범위를 담아야 하기 때문이다. 11 시료를 모두 썼다.</t>
+          <t>5. 기구 조립은 500C-1차 -11.43, 500C-2차 -7.48, 500D -6.76 dB 로 낮았다. 같은 500C 가 1차와 2차에서 4 dB 나 달라진 것은 시료가 아니라 조립 편차를 가리킨다.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>7. 판정용 기준은 «실측 전체가 허용 폭 안에 담기는 중심» 으로 잡았다. 조립은 감쇠만 시키므로 상한은 조립 감쇠가 거의 없는 극단(PCB 상태)이고 하한은 실측 최저다. 그 중앙 -7.500 에서 상·하한 여유가 각 1.07 dB 로 대칭이다.</t>
+          <t>6. 이 셋을 «불량» 으로 빼지 않고 하한 산정에 썼다. 시험 판정 기준은 대표 성능이 아니라 실제로 나올 수 있는 범위를 담아야 하기 때문이다. 11 시료를 모두 썼다.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>8. 이 기준이면 실측 6 시료가 모두 통과하고, 500C-1차(-11.43)보다 1.07 dB 더 나쁜 -12.50 dB 까지 받아 준다. PCB 상태(-3.57)도 여유 3.93 으로 담긴다.</t>
+          <t>7. 판정용 기준은 «시험 대상(기구 조립) 실측의 중앙» 으로 잡았다. 상한은 실측 최고 500E(-5.15), 하한은 실측 최저 500C-1차(-11.43)이고 그 중앙 -8.293 에서 상·하한 여유가 각 1.86 dB 로 대칭이다.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>9. 기준을 이보다 낮추면 하한은 넓어지지만 상한이 깨진다. 예를 들어 500D 와 500C-1차의 중간(-9.096)으로 잡으면 조립 감쇠가 거의 없는 개체가 위로 탈락한다(상한 여유 -0.53).</t>
+          <t>8. 조립은 감쇠만 시키고 증가시키지 않으므로 실제 위험은 아래로만 흩어진다. 남는 여유를 아래에 두었다. 이 기준의 통과 하한은 -13.29 dB 로, 실측 최저보다 1.86 dB 더 나쁜 조립까지 받아 준다.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>10. 감수하는 것이 있다. 500C-1차 같은 조립 불량도 통과하므로 이 시험만으로는 조립 불량을 걸러내지 못한다. 조립 품질은 별도 수단으로 보아야 한다.</t>
+          <t>9. 위쪽도 안전하다. 조립 감쇠가 0 인 물리적 극단(= PCB 최고 -3.57)조차 여유 0.27 로 담긴다. 실측 기구 감쇠 최소는 1.51 dB(500E)이므로 실제로는 4 배 이상 여유가 있다.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="2" t="inlineStr">
         <is>
+          <t>9-1. 기준을 이보다 더 낮추면 그 안전망을 잃는다. -9.000 으로 잡으면 조립 감쇠가 거의 없는 개체가 위로 탈락한다(여유 -0.43).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>10. 감수하는 것이 있다. 500C-1차 같은 조립 불량도 통과하므로 이 시험만으로는 조립 불량을 걸러내지 못한다. 조립 품질은 별도 수단으로 보아야 한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>11. 원본 시트에서 측정값이 헤더보다 한 행 아래에 있어 바로잡아 읽었다. 음압 값 14 개와 측정 행 14 개가 맞고, 4 행에는 값이 없으며 18 행에는 음압이 없다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="B38:G38"/>
     <mergeCell ref="B34:G34"/>
     <mergeCell ref="B39:G39"/>
     <mergeCell ref="B36:G36"/>
     <mergeCell ref="B37:G37"/>
     <mergeCell ref="B31:G31"/>
+    <mergeCell ref="B41:G41"/>
     <mergeCell ref="B32:G32"/>
     <mergeCell ref="B35:G35"/>
+    <mergeCell ref="B40:G40"/>
     <mergeCell ref="B30:G30"/>
-    <mergeCell ref="B29:G29"/>
     <mergeCell ref="B33:G33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/참고/인허가/사운드1/[참고] Sound1 입력 음압 대비 ADC 출력 테이블.xlsx
+++ b/docs/참고/인허가/사운드1/[참고] Sound1 입력 음압 대비 ADC 출력 테이블.xlsx
@@ -490,12 +490,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="52" customHeight="1">
+    <row r="4" ht="68" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>1.5세대와 Sound1 은 같은 스펙의 마이크를 쓴다. 그래서 1.5세대 테이블의 생성 규칙을 그대로 두고 Sound1 의 실측 감쇠만 반영했다.
-ADC = round(262143 x 10^((dB SPL - 120 + 감쇠) / 20)),  262143 = 2^18 - 1
-감쇠는 고음압 평탄 구간(80~110 dB SPL) 실측 평균이다. PCB 상태 -3.644 dB (5 시료), 기구 조립 -8.293 dB (3 시료).</t>
+          <t>1.5세대와 Sound1 은 같은 스펙의 마이크를 쓴다. 그래서 1.5세대 테이블의 생성 규칙을 그대로 두고 Sound1 의 감쇠만 반영했다.
+ADC = floor(262143 x 10^((dB SPL - 120 + 감쇠) / 20)),  262143 = 2^18 - 1  (1.5세대 표가 내림으로 만들어져 있다)
+감쇠는 고음압 평탄 구간(80~110 dB SPL) 실측에서 구했다.  PCB 상태 -3.644 dB = 5 시료 평균 (참조용, 시험 대상이 아니다)
+기구 조립 -8.293 dB = 실측 6 시료의 상·하한 중앙 (판정용).  시험 허용 오차 +-5 dB 는 이 표에서 정확히 한 칸 위/아래다.</t>
         </is>
       </c>
     </row>
